--- a/0 zombie type/阳光模型/13 DE 半花 hqyx/2.1阳光信息.xlsx
+++ b/0 zombie type/阳光模型/13 DE 半花 hqyx/2.1阳光信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18855" windowHeight="9270" activeTab="6"/>
+    <workbookView windowWidth="21000" windowHeight="13905" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="70">
   <si>
     <t>flag</t>
   </si>
@@ -188,19 +188,13 @@
     <t>Intercept</t>
   </si>
   <si>
-    <t>密度</t>
-  </si>
-  <si>
-    <t>红眼:舞王</t>
-  </si>
-  <si>
     <t>红眼:白眼</t>
   </si>
   <si>
     <t>橄榄:冰车</t>
   </si>
   <si>
-    <t>橄榄:密度</t>
+    <t>红眼:冰车</t>
   </si>
   <si>
     <t>p2</t>
@@ -1621,7 +1615,7 @@
                   <c:v>10401.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11210.4</c:v>
+                  <c:v>10210.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>10194.6</c:v>
@@ -1727,97 +1721,97 @@
                   <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5726.57288135593</c:v>
+                  <c:v>5395.1375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5640.43389830508</c:v>
+                  <c:v>5177.775</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6014.25254237288</c:v>
+                  <c:v>5319.7875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6657.77457627118</c:v>
+                  <c:v>5755.55</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7208.18220338983</c:v>
+                  <c:v>6513.1875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7328.39915254237</c:v>
+                  <c:v>6786.45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8714.08220338982</c:v>
+                  <c:v>7815.9625</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8575.82457627118</c:v>
+                  <c:v>7720.475</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8956.31694915253</c:v>
+                  <c:v>7862.4875</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8414.56355932203</c:v>
+                  <c:v>7763.875</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9216.03050847457</c:v>
+                  <c:v>8671.5125</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9822.15847457626</c:v>
+                  <c:v>8413.525</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9273.7313559322</c:v>
+                  <c:v>8314.9125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9022.86779661017</c:v>
+                  <c:v>8047.55</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9857.38559322033</c:v>
+                  <c:v>8814.5625</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10267.856779661</c:v>
+                  <c:v>8987.825</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9598.9847457627</c:v>
+                  <c:v>8236.0875</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>10129.9008474576</c:v>
+                  <c:v>9062.475</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9960.81694915253</c:v>
+                  <c:v>9235.7375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9663.44915254236</c:v>
+                  <c:v>8724.625</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>10093.4118644068</c:v>
+                  <c:v>8829.1375</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8400.38728813559</c:v>
+                  <c:v>7314.9</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9239.56610169491</c:v>
+                  <c:v>7881.9125</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9407.55847457627</c:v>
+                  <c:v>7795.8</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>10873.8559322034</c:v>
+                  <c:v>9234.6875</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>12346.5093220339</c:v>
+                  <c:v>10795.45</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>11544.4805084746</c:v>
+                  <c:v>10265.5875</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>12750.5025423729</c:v>
+                  <c:v>11835.725</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>13845.2957627118</c:v>
+                  <c:v>13033.9875</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>14792.8432203389</c:v>
+                  <c:v>14235.375</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>14185.6237288135</c:v>
+                  <c:v>14018.0125</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>12894.4</c:v>
@@ -1880,7 +1874,7 @@
         <c:axId val="495685896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="7000"/>
+          <c:min val="4000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2113,10 +2107,10 @@
                   <c:v>1450</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-825</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>-75</c:v>
@@ -2228,100 +2222,100 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>917.372881355932</c:v>
+                  <c:v>585.9375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>104.661016949152</c:v>
+                  <c:v>-26.5625000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>564.618644067796</c:v>
+                  <c:v>332.8125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>834.322033898306</c:v>
+                  <c:v>626.5625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>741.207627118643</c:v>
+                  <c:v>948.4375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>311.016949152542</c:v>
+                  <c:v>464.0625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1576.48305084745</c:v>
+                  <c:v>1220.3125</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52.5423728813563</c:v>
+                  <c:v>95.3124999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>571.292372881356</c:v>
-                </c:pt>
-                <c:pt idx="9" c:formatCode="0.00_ ">
-                  <c:v>-350.953389830508</c:v>
+                  <c:v>332.8125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>92.1874999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>992.266949152541</c:v>
+                  <c:v>1098.4375</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>796.927966101694</c:v>
-                </c:pt>
-                <c:pt idx="12" c:formatCode="0.00_ ">
-                  <c:v>-357.627118644067</c:v>
+                  <c:v>-67.1874999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>92.1875000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-60.0635593220342</c:v>
+                  <c:v>-76.5624999999997</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1025.31779661016</c:v>
+                  <c:v>957.8125</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>601.271186440677</c:v>
+                  <c:v>364.062499999999</c:v>
                 </c:pt>
                 <c:pt idx="16" c:formatCode="0.00_ ">
-                  <c:v>-478.072033898305</c:v>
+                  <c:v>-560.9375</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>721.716101694915</c:v>
+                  <c:v>1017.1875</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.7161016949149</c:v>
+                  <c:v>364.062499999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-106.56779661017</c:v>
+                  <c:v>-320.312499999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>620.762711864405</c:v>
+                  <c:v>295.3125</c:v>
                 </c:pt>
                 <c:pt idx="21" c:formatCode="0.00_ ">
-                  <c:v>-1502.22457627118</c:v>
+                  <c:v>-1323.4375</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1029.97881355932</c:v>
+                  <c:v>757.8125</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>358.792372881356</c:v>
+                  <c:v>104.687499999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1657.09745762711</c:v>
+                  <c:v>1629.6875</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1663.4533898305</c:v>
+                  <c:v>1751.5625</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-611.228813559322</c:v>
+                  <c:v>-339.062499999999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1396.8220338983</c:v>
+                  <c:v>1760.9375</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1285.59322033898</c:v>
+                  <c:v>1389.0625</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1138.34745762711</c:v>
+                  <c:v>1392.1875</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-416.419491525423</c:v>
+                  <c:v>-26.5624999999998</c:v>
                 </c:pt>
                 <c:pt idx="31" c:formatCode="0.00_ ">
-                  <c:v>-1100.42372881355</c:v>
+                  <c:v>-932.8125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4848,7 +4842,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C13" s="39">
         <v>1</v>
@@ -4916,7 +4910,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="6">
-        <v>-825</v>
+        <v>175</v>
       </c>
       <c r="C14" s="39">
         <v>1</v>
@@ -6395,7 +6389,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="6">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6403,7 +6397,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="6">
-        <v>-825</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6724,7 +6718,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A2:E23"/>
+  <dimension ref="A2:E21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.5" style="19"/>
@@ -6735,10 +6729,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20">
-        <v>0</v>
-      </c>
+      <c r="A2" s="20">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20"/>
       <c r="E2" s="19" t="s">
         <v>49</v>
       </c>
@@ -6749,17 +6743,17 @@
       </c>
       <c r="B3" s="22">
         <f>C3+D3</f>
-        <v>232.452119</v>
+        <v>246.7</v>
       </c>
       <c r="C3" s="22">
-        <v>423.252119</v>
+        <v>437.5</v>
       </c>
       <c r="D3" s="19">
         <v>-190.8</v>
       </c>
       <c r="E3" s="19">
         <f>B3</f>
-        <v>232.452119</v>
+        <v>246.7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6767,11 +6761,11 @@
         <v>20</v>
       </c>
       <c r="B4" s="23">
-        <v>-121.027542</v>
+        <v>-103.125</v>
       </c>
       <c r="E4" s="19">
-        <f>B4*(2*B17-1)</f>
-        <v>-7.11926603738784</v>
+        <f>B4*(2*B15-1)</f>
+        <v>-6.0661755</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6779,11 +6773,11 @@
         <v>7</v>
       </c>
       <c r="B5" s="23">
-        <v>-339.777542</v>
+        <v>-321.875</v>
       </c>
       <c r="E5" s="19">
-        <f>B5*(2*B17-1)</f>
-        <v>-19.9869110373878</v>
+        <f>B5*(2*B15-1)</f>
+        <v>-18.9338205</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6791,11 +6785,11 @@
         <v>10</v>
       </c>
       <c r="B6" s="23">
-        <v>-323.622881</v>
+        <v>-246.875</v>
       </c>
       <c r="E6" s="19">
-        <f>B6*(2*B17-1)</f>
-        <v>-19.0366370129611</v>
+        <f>B6*(2*B15-1)</f>
+        <v>-14.5220565</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6803,11 +6797,11 @@
         <v>13</v>
       </c>
       <c r="B7" s="23">
-        <v>-439.247881</v>
+        <v>-487.5</v>
       </c>
       <c r="E7" s="19">
-        <f>B7*(2*B17-1)</f>
-        <v>-25.8381065129611</v>
+        <f>B7*(2*B15-1)</f>
+        <v>-28.676466</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6815,11 +6809,11 @@
         <v>8</v>
       </c>
       <c r="B8" s="23">
-        <v>-241.340042</v>
+        <v>-160.9375</v>
       </c>
       <c r="E8" s="19">
-        <f>B8*(2*B17-1)</f>
-        <v>-14.1964707873878</v>
+        <f>B8*(2*B15-1)</f>
+        <v>-9.46691025</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6827,11 +6821,11 @@
         <v>19</v>
       </c>
       <c r="B9" s="23">
-        <v>202.409958</v>
+        <v>157.8125</v>
       </c>
       <c r="E9" s="19">
-        <f>B9*(2*B17-1)</f>
-        <v>11.9064662126122</v>
+        <f>B9*(2*B15-1)</f>
+        <v>9.28308675</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6839,11 +6833,11 @@
         <v>51</v>
       </c>
       <c r="B10" s="23">
-        <v>-113.983051</v>
+        <v>-182.8125</v>
       </c>
       <c r="E10" s="19">
-        <f>B10*(2*B22-1)</f>
-        <v>91.1864408</v>
+        <f>B10*(2*B17-1)</f>
+        <v>10.75367475</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6851,11 +6845,11 @@
         <v>52</v>
       </c>
       <c r="B11" s="23">
-        <v>-137.685381</v>
+        <v>-165.625</v>
       </c>
       <c r="E11" s="19">
-        <f>B11*(2*B19-1)</f>
-        <v>8.09913876296112</v>
+        <f>B11*(2*B17-1)</f>
+        <v>9.7426455</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6863,41 +6857,33 @@
         <v>53</v>
       </c>
       <c r="B12" s="19">
-        <v>-134.560381</v>
+        <v>140.625</v>
       </c>
       <c r="E12" s="19">
-        <f>B12*(2*B19-1)</f>
-        <v>7.91531526296112</v>
+        <f>B12*(2*B17-1)</f>
+        <v>-8.2720575</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="19">
-        <v>-246.027542</v>
-      </c>
       <c r="E13" s="19">
-        <f>B13*(2*B19-1)</f>
-        <v>14.4722060373878</v>
+        <f>SUM(E3:E12)</f>
+        <v>190.54192075</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="19">
+        <v>0.26470588</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="19">
-        <v>-143.220339</v>
-      </c>
-      <c r="E14" s="19">
-        <f>B14*(2*B23-1)</f>
-        <v>6.73977958045863</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="E15" s="19">
-        <f>SUM(E3:E14)</f>
-        <v>286.594074268295</v>
+      <c r="B15" s="19">
+        <v>0.52941176</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6905,7 +6891,8 @@
         <v>56</v>
       </c>
       <c r="B16" s="19">
-        <v>0.26470588</v>
+        <f>1+B14-2*B15</f>
+        <v>0.20588236</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6913,7 +6900,8 @@
         <v>57</v>
       </c>
       <c r="B17" s="19">
-        <v>0.52941176</v>
+        <f>B14+B16</f>
+        <v>0.47058824</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6921,42 +6909,24 @@
         <v>58</v>
       </c>
       <c r="B18" s="19">
-        <f>1+B16-2*B17</f>
-        <v>0.20588236</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="19">
-        <f>B16+B18</f>
-        <v>0.47058824</v>
+        <f>1-B17</f>
+        <v>0.52941176</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="19">
-        <f>1-B19</f>
-        <v>0.52941176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="19">
-        <f>B22*B17+(1-B17)*(1-B22)</f>
+      <c r="B21" s="19">
+        <f>B20*B15+(1-B15)*(1-B20)</f>
         <v>0.476470592</v>
       </c>
     </row>
@@ -6981,16 +6951,16 @@
   <sheetData>
     <row r="1" ht="14.25" spans="1:5">
       <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="C1" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
@@ -7016,11 +6986,11 @@
         <v>5834.2</v>
       </c>
       <c r="D3" s="13">
-        <v>917.372881355932</v>
+        <v>585.9375</v>
       </c>
       <c r="E3" s="9">
         <f>E2+D3-190.8</f>
-        <v>5726.57288135593</v>
+        <v>5395.1375</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7035,11 +7005,11 @@
         <v>5743.4</v>
       </c>
       <c r="D4" s="13">
-        <v>104.661016949152</v>
+        <v>-26.5625000000001</v>
       </c>
       <c r="E4" s="9">
         <f t="shared" ref="E3:E34" si="1">E3+D4-190.8</f>
-        <v>5640.43389830508</v>
+        <v>5177.775</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7054,11 +7024,11 @@
         <v>6377.6</v>
       </c>
       <c r="D5" s="13">
-        <v>564.618644067796</v>
+        <v>332.8125</v>
       </c>
       <c r="E5" s="9">
         <f t="shared" si="1"/>
-        <v>6014.25254237288</v>
+        <v>5319.7875</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7073,11 +7043,11 @@
         <v>6911.8</v>
       </c>
       <c r="D6" s="13">
-        <v>834.322033898306</v>
+        <v>626.5625</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="1"/>
-        <v>6657.77457627118</v>
+        <v>5755.55</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7092,11 +7062,11 @@
         <v>7771</v>
       </c>
       <c r="D7" s="13">
-        <v>741.207627118643</v>
+        <v>948.4375</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="1"/>
-        <v>7208.18220338983</v>
+        <v>6513.1875</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7111,11 +7081,11 @@
         <v>7880.2</v>
       </c>
       <c r="D8" s="13">
-        <v>311.016949152542</v>
+        <v>464.0625</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="1"/>
-        <v>7328.39915254237</v>
+        <v>6786.45</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7130,11 +7100,11 @@
         <v>9164.4</v>
       </c>
       <c r="D9" s="13">
-        <v>1576.48305084745</v>
+        <v>1220.3125</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="1"/>
-        <v>8714.08220338982</v>
+        <v>7815.9625</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7149,11 +7119,11 @@
         <v>8923.6</v>
       </c>
       <c r="D10" s="13">
-        <v>52.5423728813563</v>
+        <v>95.3124999999999</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="1"/>
-        <v>8575.82457627118</v>
+        <v>7720.475</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:5">
@@ -7168,11 +7138,11 @@
         <v>8932.8</v>
       </c>
       <c r="D11" s="13">
-        <v>571.292372881356</v>
+        <v>332.8125</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" si="1"/>
-        <v>8956.31694915253</v>
+        <v>7862.4875</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7186,12 +7156,12 @@
         <f t="shared" si="0"/>
         <v>9142</v>
       </c>
-      <c r="D12" s="16">
-        <v>-350.953389830508</v>
+      <c r="D12" s="13">
+        <v>92.1874999999999</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="1"/>
-        <v>8414.56355932203</v>
+        <v>7763.875</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7206,11 +7176,11 @@
         <v>10401.2</v>
       </c>
       <c r="D13" s="13">
-        <v>992.266949152541</v>
+        <v>1098.4375</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="1"/>
-        <v>9216.03050847457</v>
+        <v>8671.5125</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7218,18 +7188,18 @@
         <v>24</v>
       </c>
       <c r="B14" s="9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C14" s="9">
         <f t="shared" si="0"/>
-        <v>11210.4</v>
+        <v>10210.4</v>
       </c>
       <c r="D14" s="13">
-        <v>796.927966101694</v>
+        <v>-67.1874999999997</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="1"/>
-        <v>9822.15847457626</v>
+        <v>8413.525</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7237,18 +7207,18 @@
         <v>25</v>
       </c>
       <c r="B15" s="9">
-        <v>-825</v>
+        <v>175</v>
       </c>
       <c r="C15" s="9">
         <f t="shared" si="0"/>
         <v>10194.6</v>
       </c>
-      <c r="D15" s="16">
-        <v>-357.627118644067</v>
+      <c r="D15" s="13">
+        <v>92.1875000000002</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="1"/>
-        <v>9273.7313559322</v>
+        <v>8314.9125</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7263,11 +7233,11 @@
         <v>9928.8</v>
       </c>
       <c r="D16" s="13">
-        <v>-60.0635593220342</v>
+        <v>-76.5624999999997</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="1"/>
-        <v>9022.86779661017</v>
+        <v>8047.55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7282,11 +7252,11 @@
         <v>10763</v>
       </c>
       <c r="D17" s="13">
-        <v>1025.31779661016</v>
+        <v>957.8125</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="1"/>
-        <v>9857.38559322033</v>
+        <v>8814.5625</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7301,11 +7271,11 @@
         <v>11122.2</v>
       </c>
       <c r="D18" s="13">
-        <v>601.271186440677</v>
+        <v>364.062499999999</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="1"/>
-        <v>10267.856779661</v>
+        <v>8987.825</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:5">
@@ -7320,11 +7290,11 @@
         <v>10931.4</v>
       </c>
       <c r="D19" s="16">
-        <v>-478.072033898305</v>
+        <v>-560.9375</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="1"/>
-        <v>9598.9847457627</v>
+        <v>8236.0875</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7339,11 +7309,11 @@
         <v>11540.6</v>
       </c>
       <c r="D20" s="13">
-        <v>721.716101694915</v>
+        <v>1017.1875</v>
       </c>
       <c r="E20" s="9">
         <f t="shared" si="1"/>
-        <v>10129.9008474576</v>
+        <v>9062.475</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7358,11 +7328,11 @@
         <v>11524.8</v>
       </c>
       <c r="D21" s="13">
-        <v>21.7161016949149</v>
+        <v>364.062499999999</v>
       </c>
       <c r="E21" s="9">
         <f t="shared" si="1"/>
-        <v>9960.81694915253</v>
+        <v>9235.7375</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7377,11 +7347,11 @@
         <v>11059</v>
       </c>
       <c r="D22" s="13">
-        <v>-106.56779661017</v>
+        <v>-320.312499999999</v>
       </c>
       <c r="E22" s="9">
         <f t="shared" si="1"/>
-        <v>9663.44915254236</v>
+        <v>8724.625</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7396,11 +7366,11 @@
         <v>10893.2</v>
       </c>
       <c r="D23" s="13">
-        <v>620.762711864405</v>
+        <v>295.3125</v>
       </c>
       <c r="E23" s="9">
         <f t="shared" si="1"/>
-        <v>10093.4118644068</v>
+        <v>8829.1375</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7415,11 +7385,11 @@
         <v>9527.40000000001</v>
       </c>
       <c r="D24" s="16">
-        <v>-1502.22457627118</v>
+        <v>-1323.4375</v>
       </c>
       <c r="E24" s="9">
         <f t="shared" si="1"/>
-        <v>8400.38728813559</v>
+        <v>7314.9</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:5">
@@ -7434,11 +7404,11 @@
         <v>10461.6</v>
       </c>
       <c r="D25" s="13">
-        <v>1029.97881355932</v>
+        <v>757.8125</v>
       </c>
       <c r="E25" s="9">
         <f t="shared" si="1"/>
-        <v>9239.56610169491</v>
+        <v>7881.9125</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7453,11 +7423,11 @@
         <v>10495.8</v>
       </c>
       <c r="D26" s="13">
-        <v>358.792372881356</v>
+        <v>104.687499999999</v>
       </c>
       <c r="E26" s="9">
         <f t="shared" si="1"/>
-        <v>9407.55847457627</v>
+        <v>7795.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7472,11 +7442,11 @@
         <v>11755</v>
       </c>
       <c r="D27" s="13">
-        <v>1657.09745762711</v>
+        <v>1629.6875</v>
       </c>
       <c r="E27" s="9">
         <f t="shared" si="1"/>
-        <v>10873.8559322034</v>
+        <v>9234.6875</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7491,11 +7461,11 @@
         <v>13139.2</v>
       </c>
       <c r="D28" s="13">
-        <v>1663.4533898305</v>
+        <v>1751.5625</v>
       </c>
       <c r="E28" s="9">
         <f t="shared" si="1"/>
-        <v>12346.5093220339</v>
+        <v>10795.45</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7510,11 +7480,11 @@
         <v>11948.4</v>
       </c>
       <c r="D29" s="13">
-        <v>-611.228813559322</v>
+        <v>-339.062499999999</v>
       </c>
       <c r="E29" s="9">
         <f t="shared" si="1"/>
-        <v>11544.4805084746</v>
+        <v>10265.5875</v>
       </c>
     </row>
     <row r="30" ht="14.25" spans="1:5">
@@ -7529,11 +7499,11 @@
         <v>13282.6</v>
       </c>
       <c r="D30" s="13">
-        <v>1396.8220338983</v>
+        <v>1760.9375</v>
       </c>
       <c r="E30" s="9">
         <f t="shared" si="1"/>
-        <v>12750.5025423729</v>
+        <v>11835.725</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7548,11 +7518,11 @@
         <v>14291.8</v>
       </c>
       <c r="D31" s="13">
-        <v>1285.59322033898</v>
+        <v>1389.0625</v>
       </c>
       <c r="E31" s="9">
         <f t="shared" si="1"/>
-        <v>13845.2957627118</v>
+        <v>13033.9875</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7567,11 +7537,11 @@
         <v>15376</v>
       </c>
       <c r="D32" s="13">
-        <v>1138.34745762711</v>
+        <v>1392.1875</v>
       </c>
       <c r="E32" s="9">
         <f t="shared" si="1"/>
-        <v>14792.8432203389</v>
+        <v>14235.375</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="1:5">
@@ -7586,11 +7556,11 @@
         <v>14560.2</v>
       </c>
       <c r="D33" s="13">
-        <v>-416.419491525423</v>
+        <v>-26.5624999999998</v>
       </c>
       <c r="E33" s="9">
         <f t="shared" si="1"/>
-        <v>14185.6237288135</v>
+        <v>14018.0125</v>
       </c>
     </row>
     <row r="34" ht="14.25" spans="1:5">
@@ -7605,7 +7575,7 @@
         <v>12894.4</v>
       </c>
       <c r="D34" s="16">
-        <v>-1100.42372881355</v>
+        <v>-932.8125</v>
       </c>
       <c r="E34" s="9">
         <f t="shared" si="1"/>
@@ -7704,7 +7674,7 @@
         <v>21</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="1" spans="1:23">
@@ -10049,43 +10019,43 @@
     <row r="1" s="1" customFormat="1" spans="2:4">
       <c r="B1" s="2"/>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="2:4">
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D2" s="2">
-        <v>-325</v>
+        <v>-255</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="2:4">
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="2">
-        <v>-175</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:4">
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4">
-        <v>0.13</v>
+        <v>1.17</v>
       </c>
       <c r="D4" s="2">
-        <v>-100</v>
+        <v>-40</v>
       </c>
     </row>
   </sheetData>
